--- a/prix/basin.xlsx
+++ b/prix/basin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\peintures\prix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB369544-6077-449C-8C9E-3834B0C24DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4920E04B-6475-415B-8764-8BE5FD7A9FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="19416" windowHeight="11016" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
+    <workbookView xWindow="23340" yWindow="0" windowWidth="19116" windowHeight="10884" xr2:uid="{6E95DC93-531D-460D-9A06-44397A8920D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -923,13 +923,13 @@
         <v>62</v>
       </c>
       <c r="D12" s="13">
-        <v>95.83</v>
+        <v>98.710000000000008</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>45</v>
       </c>
       <c r="F12" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -943,13 +943,13 @@
         <v>8</v>
       </c>
       <c r="D13" s="13">
-        <v>183.18</v>
+        <v>188.69</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>46</v>
       </c>
       <c r="F13" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -983,13 +983,13 @@
         <v>62</v>
       </c>
       <c r="D15" s="13">
-        <v>205.25</v>
+        <v>211.44</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>48</v>
       </c>
       <c r="F15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1103,7 +1103,7 @@
         <v>54</v>
       </c>
       <c r="F21" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -1123,7 +1123,7 @@
         <v>55</v>
       </c>
       <c r="F22" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -1217,13 +1217,13 @@
         <v>6</v>
       </c>
       <c r="D27" s="13">
-        <v>48.18</v>
+        <v>46.81</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>60</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
